--- a/generated_strict_test_data/Mixed/Config.xlsx
+++ b/generated_strict_test_data/Mixed/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\madha\Desktop\attainment_software\generated_strict_test_data\Mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8793A3A8-DA25-42A0-830E-074EA632C3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3153EC8F-0B36-4FF4-B4EB-3C1A613D39E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="360" windowWidth="25440" windowHeight="15270" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1581,7 +1581,7 @@
         <v>64</v>
       </c>
       <c r="B2">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1589,7 +1589,7 @@
         <v>65</v>
       </c>
       <c r="B3">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
